--- a/public/data/monthly-revenue-11505.xlsx
+++ b/public/data/monthly-revenue-11505.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -457,40 +457,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3580</v>
+        <v>友威科</v>
       </c>
       <c r="B2" t="str">
         <v>友威科</v>
       </c>
       <c r="C2" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>11505</v>
       </c>
       <c r="E2" t="str">
-        <v>34,457</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>40,296</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>-5,839</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>-14.49</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>146,267</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>159,437</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v>-13,170</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>-8.26</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -498,40 +498,40 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>3675</v>
+        <v>德微</v>
       </c>
       <c r="B3" t="str">
         <v>德微</v>
       </c>
       <c r="C3" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>11505</v>
       </c>
       <c r="E3" t="str">
-        <v>267,072</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>214,657</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>52,415</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>24.42</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>1,205,539</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>1,053,074</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>152,465</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v>14.48</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -539,40 +539,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6414</v>
+        <v>樺漢</v>
       </c>
       <c r="B4" t="str">
         <v>樺漢</v>
       </c>
       <c r="C4" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>11505</v>
       </c>
       <c r="E4" t="str">
-        <v>15,579,250</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>11,517,071</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4,062,179</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>35.27</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>67,632,029</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>57,907,159</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>9,724,870</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>16.79</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -580,40 +580,40 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6416</v>
+        <v>瑞祺電通</v>
       </c>
       <c r="B5" t="str">
         <v>瑞祺電通</v>
       </c>
       <c r="C5" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v>11505</v>
       </c>
       <c r="E5" t="str">
-        <v>349,990</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>300,423</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>49,567</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>16.50</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>1,723,027</v>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <v>1,749,392</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>-26,365</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>-1.51</v>
+        <v/>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -621,122 +621,122 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3305</v>
+        <v>昇貿</v>
       </c>
       <c r="B6" t="str">
         <v>昇貿</v>
       </c>
       <c r="C6" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>11505</v>
       </c>
       <c r="E6" t="str">
-        <v>1,348,799</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>787,091</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>561,708</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>71.37</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>6,539,123</v>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <v>4,030,299</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>2,508,824</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>62.25</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>銷售量增加及原料價格上漲</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>8098</v>
+        <v>慶康科技</v>
       </c>
       <c r="B7" t="str">
         <v>慶康科技</v>
       </c>
       <c r="C7" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v>11505</v>
       </c>
       <c r="E7" t="str">
-        <v>71,937</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>40,333</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>31,604</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>78.36</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>282,191</v>
+        <v/>
       </c>
       <c r="J7" t="str">
-        <v>262,735</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>19,456</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>7.41</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>因客戶終端需求增加，故本期營收隨之增加。</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>9958</v>
+        <v>世紀鋼</v>
       </c>
       <c r="B8" t="str">
         <v>世紀鋼</v>
       </c>
       <c r="C8" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v>11505</v>
       </c>
       <c r="E8" t="str">
-        <v>1,708,140</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>1,324,362</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>383,778</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>28.98</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>8,042,587</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>6,577,976</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>1,464,611</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>22.27</v>
+        <v/>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -744,40 +744,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6672</v>
+        <v>騰輝電子-KY</v>
       </c>
       <c r="B9" t="str">
         <v>騰輝電子-KY</v>
       </c>
       <c r="C9" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D9" t="str">
         <v>11505</v>
       </c>
       <c r="E9" t="str">
-        <v>530,395</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>392,926</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>137,469</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>34.99</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>2,286,223</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>1,784,310</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>501,913</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v>28.13</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1560</v>
+        <v>中砂</v>
       </c>
       <c r="B10" t="str">
         <v>中砂</v>
       </c>
       <c r="C10" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v>11505</v>
       </c>
       <c r="E10" t="str">
-        <v>829,267</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>704,078</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>125,189</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>17.78</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>3,952,897</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v>3,174,566</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>778,331</v>
+        <v/>
       </c>
       <c r="L10" t="str">
-        <v>24.52</v>
+        <v/>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,40 +826,40 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>3138</v>
+        <v>耀登</v>
       </c>
       <c r="B11" t="str">
         <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v>11505</v>
       </c>
       <c r="E11" t="str">
-        <v>139,198</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>130,227</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>8,971</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>6.89</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>703,765</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>598,847</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>104,918</v>
+        <v/>
       </c>
       <c r="L11" t="str">
-        <v>17.52</v>
+        <v/>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -867,81 +867,81 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4768</v>
+        <v>材料*-KY</v>
       </c>
       <c r="B12" t="str">
-        <v>晶呈科技</v>
+        <v>材料*-KY</v>
       </c>
       <c r="C12" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D12" t="str">
         <v>11505</v>
       </c>
       <c r="E12" t="str">
-        <v>97,605</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>59,427</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>38,178</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>64.24</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>712,530</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>290,274</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>422,256</v>
+        <v/>
       </c>
       <c r="L12" t="str">
-        <v>145.47</v>
+        <v/>
       </c>
       <c r="M12" t="str">
-        <v>本月營收較去年同期增加乃因客戶需求增加</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5536</v>
+        <v>晶呈科技</v>
       </c>
       <c r="B13" t="str">
-        <v>聖暉*</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C13" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D13" t="str">
         <v>11505</v>
       </c>
       <c r="E13" t="str">
-        <v>4,518,885</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>3,535,929</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>982,956</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>27.80</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>20,210,116</v>
+        <v/>
       </c>
       <c r="J13" t="str">
-        <v>15,641,518</v>
+        <v/>
       </c>
       <c r="K13" t="str">
-        <v>4,568,598</v>
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v>29.21</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -949,40 +949,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5543</v>
+        <v>聖暉*</v>
       </c>
       <c r="B14" t="str">
-        <v>桓鼎-KY</v>
+        <v>聖暉*</v>
       </c>
       <c r="C14" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D14" t="str">
         <v>11505</v>
       </c>
       <c r="E14" t="str">
-        <v>268,772</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>289,607</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>-20,835</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>-7.19</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>1,401,603</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v>1,327,770</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>73,833</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>5.56</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,81 +990,81 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6613</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="B15" t="str">
-        <v>朋億*</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C15" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D15" t="str">
         <v>11505</v>
       </c>
       <c r="E15" t="str">
-        <v>1,082,893</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>595,911</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>486,982</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>81.72</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>4,135,667</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>3,288,792</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>846,875</v>
+        <v/>
       </c>
       <c r="L15" t="str">
-        <v>25.75</v>
+        <v/>
       </c>
       <c r="M15" t="str">
-        <v>營收較去年同期增加主係半導體廠擴廠暢旺</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>6977</v>
+        <v>朋億*</v>
       </c>
       <c r="B16" t="str">
-        <v>聯純</v>
+        <v>朋億*</v>
       </c>
       <c r="C16" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D16" t="str">
         <v>11505</v>
       </c>
       <c r="E16" t="str">
-        <v>139,988</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>151,613</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>-11,625</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>-7.67</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>625,491</v>
+        <v/>
       </c>
       <c r="J16" t="str">
-        <v>909,225</v>
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>-283,734</v>
+        <v/>
       </c>
       <c r="L16" t="str">
-        <v>-31.21</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1072,40 +1072,40 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>6938</v>
+        <v>聯純</v>
       </c>
       <c r="B17" t="str">
-        <v>藍新資訊</v>
+        <v>聯純</v>
       </c>
       <c r="C17" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D17" t="str">
         <v>11505</v>
       </c>
       <c r="E17" t="str">
-        <v>43,565</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>32,914</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>10,651</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>32.36</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>237,267</v>
+        <v/>
       </c>
       <c r="J17" t="str">
-        <v>203,893</v>
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>33,374</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>16.37</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,40 +1113,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2248</v>
+        <v>藍新資訊</v>
       </c>
       <c r="B18" t="str">
-        <v>華勝-KY</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C18" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D18" t="str">
         <v>11505</v>
       </c>
       <c r="E18" t="str">
-        <v>197,831</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>149,714</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>48,117</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>32.14</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>1,024,404</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v>751,823</v>
+        <v/>
       </c>
       <c r="K18" t="str">
-        <v>272,581</v>
+        <v/>
       </c>
       <c r="L18" t="str">
-        <v>36.26</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>7455</v>
+        <v>華勝-KY</v>
       </c>
       <c r="B19" t="str">
-        <v>樺緯物聯</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C19" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D19" t="str">
         <v>11505</v>
       </c>
       <c r="E19" t="str">
-        <v>53,328</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>65,854</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>-12,526</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>-19.02</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>246,750</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v>342,773</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>-96,023</v>
+        <v/>
       </c>
       <c r="L19" t="str">
-        <v>-28.01</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,81 +1195,81 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>8045</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="B20" t="str">
-        <v>達運光電</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C20" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D20" t="str">
         <v>11505</v>
       </c>
       <c r="E20" t="str">
-        <v>113,502</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>104,111</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>9,391</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>9.02</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>802,411</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>534,443</v>
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v>267,968</v>
+        <v/>
       </c>
       <c r="L20" t="str">
-        <v>50.14</v>
+        <v/>
       </c>
       <c r="M20" t="str">
-        <v>產品品項增換</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2429</v>
+        <v>達運光電</v>
       </c>
       <c r="B21" t="str">
-        <v>銘旺科</v>
+        <v>達運光電</v>
       </c>
       <c r="C21" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D21" t="str">
         <v>11505</v>
       </c>
       <c r="E21" t="str">
-        <v>41,035</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>34,313</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>6,722</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>19.59</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>179,195</v>
+        <v/>
       </c>
       <c r="J21" t="str">
-        <v>178,691</v>
+        <v/>
       </c>
       <c r="K21" t="str">
-        <v>504</v>
+        <v/>
       </c>
       <c r="L21" t="str">
-        <v>0.28</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1277,81 +1277,81 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>8096</v>
+        <v>銘旺科</v>
       </c>
       <c r="B22" t="str">
-        <v>擎亞</v>
+        <v>銘旺科</v>
       </c>
       <c r="C22" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D22" t="str">
         <v>11505</v>
       </c>
       <c r="E22" t="str">
-        <v>3,981,347</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>1,564,353</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>2,416,994</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>154.50</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>18,511,699</v>
+        <v/>
       </c>
       <c r="J22" t="str">
-        <v>19,681,467</v>
+        <v/>
       </c>
       <c r="K22" t="str">
-        <v>-1,169,768</v>
+        <v/>
       </c>
       <c r="L22" t="str">
-        <v>-5.94</v>
+        <v/>
       </c>
       <c r="M22" t="str">
-        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>7847</v>
+        <v>擎亞</v>
       </c>
       <c r="B23" t="str">
-        <v>豊漁</v>
+        <v>擎亞</v>
       </c>
       <c r="C23" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D23" t="str">
         <v>11505</v>
       </c>
       <c r="E23" t="str">
-        <v>107,884</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>83,974</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>23,910</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>28.47</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>486,542</v>
+        <v/>
       </c>
       <c r="J23" t="str">
-        <v>415,511</v>
+        <v/>
       </c>
       <c r="K23" t="str">
-        <v>71,031</v>
+        <v/>
       </c>
       <c r="L23" t="str">
-        <v>17.09</v>
+        <v/>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1359,40 +1359,40 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4441</v>
+        <v>豊漁</v>
       </c>
       <c r="B24" t="str">
-        <v>振大環球</v>
+        <v>豊漁</v>
       </c>
       <c r="C24" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D24" t="str">
         <v>11505</v>
       </c>
       <c r="E24" t="str">
-        <v>381,811</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>589,572</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>-207,761</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>-35.24</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>3,073,136</v>
+        <v/>
       </c>
       <c r="J24" t="str">
-        <v>2,682,568</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v>390,568</v>
+        <v/>
       </c>
       <c r="L24" t="str">
-        <v>14.56</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>7854</v>
+        <v>振大環球</v>
       </c>
       <c r="B25" t="str">
-        <v>佐茂</v>
+        <v>振大環球</v>
       </c>
       <c r="C25" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D25" t="str">
         <v>11505</v>
       </c>
       <c r="E25" t="str">
-        <v>172,533</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>142,788</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>29,745</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>20.83</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>736,870</v>
+        <v/>
       </c>
       <c r="J25" t="str">
-        <v>714,583</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>22,287</v>
+        <v/>
       </c>
       <c r="L25" t="str">
-        <v>3.12</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,40 +1441,40 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2330</v>
+        <v>佐茂</v>
       </c>
       <c r="B26" t="str">
-        <v>台積電</v>
+        <v>佐茂</v>
       </c>
       <c r="C26" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D26" t="str">
         <v>11505</v>
       </c>
       <c r="E26" t="str">
-        <v>416,975,163</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v>320,515,951</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>96,459,212</v>
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>30.09</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>1,961,803,721</v>
+        <v/>
       </c>
       <c r="J26" t="str">
-        <v>1,509,336,555</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>452,467,166</v>
+        <v/>
       </c>
       <c r="L26" t="str">
-        <v>29.98</v>
+        <v/>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1482,89 +1482,130 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3135</v>
+        <v>2330</v>
       </c>
       <c r="B27" t="str">
-        <v>凌航</v>
+        <v>2330</v>
       </c>
       <c r="C27" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D27" t="str">
         <v>11505</v>
       </c>
       <c r="E27" t="str">
-        <v>1,841,758</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v>550,652</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>1,291,106</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>234.47</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>9,652,396</v>
+        <v/>
       </c>
       <c r="J27" t="str">
-        <v>2,518,803</v>
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>7,133,593</v>
+        <v/>
       </c>
       <c r="L27" t="str">
-        <v>283.21</v>
+        <v/>
       </c>
       <c r="M27" t="str">
-        <v>市場價格上漲及需求增加。</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>3135</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3135</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>11505</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>8112</v>
       </c>
-      <c r="B28" t="str">
-        <v>至上</v>
-      </c>
-      <c r="C28" t="str">
-        <v>上市公司</v>
-      </c>
-      <c r="D28" t="str">
-        <v>11505</v>
-      </c>
-      <c r="E28" t="str">
-        <v>53,921,149</v>
-      </c>
-      <c r="F28" t="str">
-        <v>15,267,382</v>
-      </c>
-      <c r="G28" t="str">
-        <v>38,653,767</v>
-      </c>
-      <c r="H28" t="str">
-        <v>253.18</v>
-      </c>
-      <c r="I28" t="str">
-        <v>199,146,786</v>
-      </c>
-      <c r="J28" t="str">
-        <v>84,065,759</v>
-      </c>
-      <c r="K28" t="str">
-        <v>115,081,027</v>
-      </c>
-      <c r="L28" t="str">
-        <v>136.89</v>
-      </c>
-      <c r="M28" t="str">
-        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
+      <c r="B29" t="str">
+        <v>8112</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>11505</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/monthly-revenue-11505.xlsx
+++ b/public/data/monthly-revenue-11505.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M28"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -457,40 +457,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>友威科</v>
+        <v>3580</v>
       </c>
       <c r="B2" t="str">
         <v>友威科</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D2" t="str">
         <v>11505</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>34,457</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>40,296</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>-5,839</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>-14.49</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>146,267</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>159,437</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>-13,170</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>-8.26</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -498,40 +498,40 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>德微</v>
+        <v>3675</v>
       </c>
       <c r="B3" t="str">
         <v>德微</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D3" t="str">
         <v>11505</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>267,072</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>214,657</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>52,415</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>24.42</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>1,205,539</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>1,053,074</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>152,465</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>14.48</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -539,40 +539,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>樺漢</v>
+        <v>6414</v>
       </c>
       <c r="B4" t="str">
         <v>樺漢</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D4" t="str">
         <v>11505</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>15,579,250</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>11,517,071</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4,062,179</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>35.27</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>67,632,029</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>57,907,159</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>9,724,870</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>16.79</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -580,40 +580,40 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>瑞祺電通</v>
+        <v>6416</v>
       </c>
       <c r="B5" t="str">
         <v>瑞祺電通</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D5" t="str">
         <v>11505</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>349,990</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>300,423</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>49,567</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>16.50</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>1,723,027</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>1,749,392</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>-26,365</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>-1.51</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -621,122 +621,122 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>昇貿</v>
+        <v>3305</v>
       </c>
       <c r="B6" t="str">
         <v>昇貿</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D6" t="str">
         <v>11505</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>1,348,799</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>787,091</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>561,708</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>71.37</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>6,539,123</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>4,030,299</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>2,508,824</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>62.25</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>銷售量增加及原料價格上漲</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>慶康科技</v>
+        <v>8098</v>
       </c>
       <c r="B7" t="str">
         <v>慶康科技</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D7" t="str">
         <v>11505</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>71,937</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>40,333</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>31,604</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>78.36</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>282,191</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>262,735</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>19,456</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>7.41</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>因客戶終端需求增加，故本期營收隨之增加。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>世紀鋼</v>
+        <v>9958</v>
       </c>
       <c r="B8" t="str">
         <v>世紀鋼</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D8" t="str">
         <v>11505</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>1,708,140</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1,324,362</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>383,778</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>28.98</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>8,042,587</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>6,577,976</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>1,464,611</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>22.27</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -744,40 +744,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>騰輝電子-KY</v>
+        <v>6672</v>
       </c>
       <c r="B9" t="str">
         <v>騰輝電子-KY</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D9" t="str">
         <v>11505</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>530,395</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>392,926</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>137,469</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>34.99</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>2,286,223</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>1,784,310</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>501,913</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>28.13</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>中砂</v>
+        <v>1560</v>
       </c>
       <c r="B10" t="str">
         <v>中砂</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D10" t="str">
         <v>11505</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>829,267</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>704,078</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>125,189</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>17.78</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>3,952,897</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>3,174,566</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>778,331</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>24.52</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,40 +826,40 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>耀登</v>
+        <v>3138</v>
       </c>
       <c r="B11" t="str">
         <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D11" t="str">
         <v>11505</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>139,198</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>130,227</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>8,971</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>6.89</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>703,765</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>598,847</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>104,918</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>17.52</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -867,81 +867,81 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>材料*-KY</v>
+        <v>4768</v>
       </c>
       <c r="B12" t="str">
-        <v>材料*-KY</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D12" t="str">
         <v>11505</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>97,605</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>59,427</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>38,178</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>64.24</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>712,530</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>290,274</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>422,256</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>145.47</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>本月營收較去年同期增加乃因客戶需求增加</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>晶呈科技</v>
+        <v>5536</v>
       </c>
       <c r="B13" t="str">
-        <v>晶呈科技</v>
+        <v>聖暉*</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D13" t="str">
         <v>11505</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>4,518,885</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>3,535,929</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>982,956</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>27.80</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>20,210,116</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>15,641,518</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>4,568,598</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>29.21</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -949,40 +949,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>聖暉*</v>
+        <v>5543</v>
       </c>
       <c r="B14" t="str">
-        <v>聖暉*</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D14" t="str">
         <v>11505</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>268,772</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>289,607</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>-20,835</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>-7.19</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>1,401,603</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>1,327,770</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>73,833</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>5.56</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,81 +990,81 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>桓鼎-KY</v>
+        <v>6613</v>
       </c>
       <c r="B15" t="str">
-        <v>桓鼎-KY</v>
+        <v>朋億*</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D15" t="str">
         <v>11505</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>1,082,893</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>595,911</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>486,982</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>81.72</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>4,135,667</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>3,288,792</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>846,875</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>25.75</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>營收較去年同期增加主係半導體廠擴廠暢旺</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>朋億*</v>
+        <v>6977</v>
       </c>
       <c r="B16" t="str">
-        <v>朋億*</v>
+        <v>聯純</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D16" t="str">
         <v>11505</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>139,988</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>151,613</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>-11,625</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>-7.67</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>625,491</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>909,225</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>-283,734</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>-31.21</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1072,40 +1072,40 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>聯純</v>
+        <v>6938</v>
       </c>
       <c r="B17" t="str">
-        <v>聯純</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D17" t="str">
         <v>11505</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>43,565</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>32,914</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>10,651</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>32.36</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>237,267</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>203,893</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>33,374</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>16.37</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,40 +1113,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>藍新資訊</v>
+        <v>2248</v>
       </c>
       <c r="B18" t="str">
-        <v>藍新資訊</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D18" t="str">
         <v>11505</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>197,831</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>149,714</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>48,117</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>32.14</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>1,024,404</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>751,823</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>272,581</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>36.26</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>華勝-KY</v>
+        <v>7455</v>
       </c>
       <c r="B19" t="str">
-        <v>華勝-KY</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D19" t="str">
         <v>11505</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>53,328</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>65,854</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>-12,526</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>-19.02</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>246,750</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>342,773</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>-96,023</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>-28.01</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,81 +1195,81 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>樺緯物聯</v>
+        <v>8045</v>
       </c>
       <c r="B20" t="str">
-        <v>樺緯物聯</v>
+        <v>達運光電</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D20" t="str">
         <v>11505</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>113,502</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>104,111</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>9,391</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>9.02</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>802,411</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>534,443</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>267,968</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>50.14</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>產品品項增換</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>達運光電</v>
+        <v>2429</v>
       </c>
       <c r="B21" t="str">
-        <v>達運光電</v>
+        <v>銘旺科</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D21" t="str">
         <v>11505</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>41,035</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>34,313</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>6,722</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>19.59</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>179,195</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>178,691</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>504</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>0.28</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1277,81 +1277,81 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>銘旺科</v>
+        <v>8096</v>
       </c>
       <c r="B22" t="str">
-        <v>銘旺科</v>
+        <v>擎亞</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D22" t="str">
         <v>11505</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>3,981,347</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>1,564,353</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>2,416,994</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>154.50</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>18,511,699</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>19,681,467</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>-1,169,768</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>-5.94</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>擎亞</v>
+        <v>7847</v>
       </c>
       <c r="B23" t="str">
-        <v>擎亞</v>
+        <v>豊漁</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D23" t="str">
         <v>11505</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>107,884</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>83,974</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>23,910</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>28.47</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>486,542</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>415,511</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>71,031</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>17.09</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1359,40 +1359,40 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>豊漁</v>
+        <v>4441</v>
       </c>
       <c r="B24" t="str">
-        <v>豊漁</v>
+        <v>振大環球</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D24" t="str">
         <v>11505</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>381,811</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>589,572</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>-207,761</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>-35.24</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>3,073,136</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>2,682,568</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>390,568</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>14.56</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>振大環球</v>
+        <v>7854</v>
       </c>
       <c r="B25" t="str">
-        <v>振大環球</v>
+        <v>佐茂</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D25" t="str">
         <v>11505</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>172,533</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>142,788</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>29,745</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>20.83</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>736,870</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>714,583</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>22,287</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>3.12</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,40 +1441,40 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>佐茂</v>
+        <v>2330</v>
       </c>
       <c r="B26" t="str">
-        <v>佐茂</v>
+        <v>台積電</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D26" t="str">
         <v>11505</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>416,975,163</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>320,515,951</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>96,459,212</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>30.09</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>1,961,803,721</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>1,509,336,555</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>452,467,166</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>29.98</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1482,130 +1482,89 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2330</v>
+        <v>3135</v>
       </c>
       <c r="B27" t="str">
-        <v>2330</v>
+        <v>凌航</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D27" t="str">
         <v>11505</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>1,841,758</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>550,652</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>1,291,106</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>234.47</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>9,652,396</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>2,518,803</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>7,133,593</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>283.21</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>市場價格上漲及需求增加。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3135</v>
+        <v>8112</v>
       </c>
       <c r="B28" t="str">
-        <v>3135</v>
+        <v>至上</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D28" t="str">
         <v>11505</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>53,921,149</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>15,267,382</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>38,653,767</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>253.18</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>199,146,786</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>84,065,759</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>115,081,027</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>136.89</v>
       </c>
       <c r="M28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>8112</v>
-      </c>
-      <c r="B29" t="str">
-        <v>8112</v>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <v>11505</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
+        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
   </ignoredErrors>
 </worksheet>
 </file>